--- a/data/trans_dic/IP16A12_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre</t>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,47</t>
+          <t>0,0; 22,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 33,0</t>
+          <t>4,43; 32,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 20,92</t>
+          <t>3,5; 20,08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 17,87</t>
+          <t>1,37; 17,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 21,39</t>
+          <t>7,2; 22,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 15,54</t>
+          <t>4,63; 16,39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 28,34</t>
+          <t>3,19; 27,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 29,23</t>
+          <t>3,02; 28,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 22,78</t>
+          <t>5,9; 21,84</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 48,08</t>
+          <t>4,79; 48,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,18; 77,75</t>
+          <t>15,97; 75,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,88; 54,82</t>
+          <t>17,5; 58,19</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 48,61</t>
+          <t>6,29; 49,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 48,89</t>
+          <t>5,34; 46,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,02; 37,75</t>
+          <t>9,69; 38,37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 52,89</t>
+          <t>16,43; 56,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,53; 34,45</t>
+          <t>9,86; 37,05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,65; 49,04</t>
+          <t>21,78; 50,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 31,47</t>
+          <t>10,72; 32,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,74; 34,57</t>
+          <t>17,05; 35,2</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 46,25</t>
+          <t>4,49; 44,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,72; 61,08</t>
+          <t>17,16; 64,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,72; 51,11</t>
+          <t>15,98; 48,72</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,61; 19,76</t>
+          <t>8,19; 19,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,64; 25,6</t>
+          <t>15,52; 25,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,8; 20,97</t>
+          <t>12,83; 20,93</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2919</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6920</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>989; 7309</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1845; 10585</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4897</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6321</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11217</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>876; 10895</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3470; 10799</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5180; 18338</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2168</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4609</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>584; 5066</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>613; 5826</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2278; 8439</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2748</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5422</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8169</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>599; 6078</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1768; 8413</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4128; 13729</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2304</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4401</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>552; 4354</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>598; 5230</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1935; 7665</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4330</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4330</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2236; 7711</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2099; 7887</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>10255</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8576</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>18831</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>6487; 15008</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4755; 14311</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>12640; 26094</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>364; 3617</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2009; 7496</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>3166; 9656</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>25669</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>36735</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>62404</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>14685; 35344</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>28349; 47133</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>46438; 75764</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A12_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,78</t>
+          <t>0,0; 21,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 32,74</t>
+          <t>3,92; 33,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 20,08</t>
+          <t>3,37; 19,69</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 17,09</t>
+          <t>1,7; 17,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 22,42</t>
+          <t>7,26; 23,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 16,39</t>
+          <t>4,37; 16,47</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 27,61</t>
+          <t>3,05; 25,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 28,72</t>
+          <t>3,71; 29,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 21,84</t>
+          <t>5,36; 22,27</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 48,54</t>
+          <t>3,32; 51,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,97; 75,97</t>
+          <t>20,4; 76,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 58,19</t>
+          <t>17,21; 56,71</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 49,61</t>
+          <t>6,24; 48,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 46,71</t>
+          <t>4,91; 46,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 38,37</t>
+          <t>11,32; 41,06</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,43; 56,67</t>
+          <t>15,77; 53,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,86; 37,05</t>
+          <t>9,17; 36,81</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,78; 50,39</t>
+          <t>20,34; 50,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 32,27</t>
+          <t>10,2; 31,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,05; 35,2</t>
+          <t>16,79; 36,04</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 44,59</t>
+          <t>4,84; 44,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,16; 64,03</t>
+          <t>18,32; 62,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,98; 48,72</t>
+          <t>17,04; 48,31</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,19; 19,71</t>
+          <t>8,51; 19,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,52; 25,8</t>
+          <t>15,04; 25,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,83; 20,93</t>
+          <t>12,46; 20,86</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6920</t>
+          <t>0; 6489</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>989; 7309</t>
+          <t>875; 7384</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1845; 10585</t>
+          <t>1777; 10378</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>876; 10895</t>
+          <t>1082; 11445</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3470; 10799</t>
+          <t>3497; 11370</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5180; 18338</t>
+          <t>4890; 18436</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>584; 5066</t>
+          <t>559; 4748</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>613; 5826</t>
+          <t>753; 6078</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2278; 8439</t>
+          <t>2070; 8602</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>599; 6078</t>
+          <t>416; 6494</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1768; 8413</t>
+          <t>2259; 8491</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4128; 13729</t>
+          <t>4061; 13381</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>552; 4354</t>
+          <t>548; 4249</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>598; 5230</t>
+          <t>550; 5200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1935; 7665</t>
+          <t>2260; 8202</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2236; 7711</t>
+          <t>2146; 7264</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2099; 7887</t>
+          <t>1952; 7836</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6487; 15008</t>
+          <t>6058; 14937</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4755; 14311</t>
+          <t>4523; 14033</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12640; 26094</t>
+          <t>12449; 26723</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>364; 3617</t>
+          <t>393; 3633</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2009; 7496</t>
+          <t>2145; 7296</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3166; 9656</t>
+          <t>3378; 9575</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>14685; 35344</t>
+          <t>15258; 35624</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28349; 47133</t>
+          <t>27471; 46478</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46438; 75764</t>
+          <t>45122; 75508</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A12_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Provincia-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,36</t>
+          <t>2,49; 32,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 33,08</t>
+          <t>0,0; 18,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 19,69</t>
+          <t>3,41; 20,26</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 17,96</t>
+          <t>6,13; 20,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 23,61</t>
+          <t>5,48; 21,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 16,47</t>
+          <t>7,52; 18,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 25,87</t>
+          <t>3,31; 28,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 29,96</t>
+          <t>3,48; 29,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 22,27</t>
+          <t>5,67; 22,97</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 51,87</t>
+          <t>20,4; 78,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 76,68</t>
+          <t>5,76; 46,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 56,71</t>
+          <t>15,28; 54,32</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 48,41</t>
+          <t>7,08; 53,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 46,44</t>
+          <t>6,28; 49,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,32; 41,06</t>
+          <t>11,12; 39,19</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31,02%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>12,35; 51,93</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>15,77; 53,38</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 36,81</t>
+          <t>7,21; 32,68</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,34; 50,15</t>
+          <t>9,87; 33,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,2; 31,64</t>
+          <t>20,65; 48,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,79; 36,04</t>
+          <t>16,83; 35,28</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,84; 44,78</t>
+          <t>16,28; 58,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,32; 62,32</t>
+          <t>4,37; 44,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,04; 48,31</t>
+          <t>15,22; 50,31</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,51; 19,86</t>
+          <t>15,48; 25,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,04; 25,44</t>
+          <t>12,06; 21,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,46; 20,86</t>
+          <t>15,24; 22,41</t>
         </is>
       </c>
     </row>
@@ -1029,18 +1029,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>3646</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6489</t>
+          <t>480; 6296</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>875; 7384</t>
+          <t>0; 3836</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1777; 10378</t>
+          <t>1368; 8119</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>9797</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1082; 11445</t>
+          <t>2615; 8789</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3497; 11370</t>
+          <t>2165; 8668</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4890; 18436</t>
+          <t>6178; 15246</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4227</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>559; 4748</t>
+          <t>585; 5031</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>753; 6078</t>
+          <t>609; 5151</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2070; 8602</t>
+          <t>1994; 8083</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>7536</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>416; 6494</t>
+          <t>2124; 8153</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2259; 8491</t>
+          <t>704; 5697</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4061; 13381</t>
+          <t>3459; 12297</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4580</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>548; 4249</t>
+          <t>727; 5530</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>550; 5200</t>
+          <t>566; 4467</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2260; 8202</t>
+          <t>2145; 7557</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3548</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>4330</t>
-        </is>
-      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>3548</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>1413; 5939</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2146; 7264</t>
-        </is>
-      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1952; 7836</t>
+          <t>1377; 6241</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>18542</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6058; 14937</t>
+          <t>4150; 14106</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4523; 14033</t>
+          <t>6252; 14620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12449; 26723</t>
+          <t>12165; 25506</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>5635</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>393; 3633</t>
+          <t>1906; 6896</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2145; 7296</t>
+          <t>334; 3362</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3378; 9575</t>
+          <t>2944; 9731</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>57510</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15258; 35624</t>
+          <t>25608; 42931</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>27471; 46478</t>
+          <t>17446; 31555</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45122; 75508</t>
+          <t>47256; 69490</t>
         </is>
       </c>
     </row>
